--- a/output/dataset_14.xlsx
+++ b/output/dataset_14.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drop width (cm)</t>
+          <t>status</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Estimated Width (μm)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Estimated Width</t>
+          <t>Measured Width (μm)</t>
         </is>
       </c>
     </row>
@@ -528,15 +528,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>3930.911865234375</v>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -571,15 +571,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>3930.21728515625</v>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -614,15 +614,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>3929.479736328125</v>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -657,15 +657,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>3929.605224609375</v>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -700,15 +700,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>3929.841796875</v>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -743,15 +743,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>3930.284912109375</v>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -786,15 +786,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>3930.304931640625</v>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -829,15 +829,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>3930.3662109375</v>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -872,15 +872,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>3932.662109375</v>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -915,15 +915,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>3933.67919921875</v>
       </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -958,15 +958,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>3934.931884765625</v>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1001,15 +1001,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>3935.69921875</v>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1044,15 +1044,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>3935.858642578125</v>
       </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1087,15 +1087,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>3935.1845703125</v>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1130,15 +1130,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>3932.95361328125</v>
       </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1173,15 +1173,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>3932.579345703125</v>
       </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1216,15 +1216,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>3933.430908203125</v>
       </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1259,15 +1259,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>3934.123046875</v>
       </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1302,15 +1302,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>3933.906005859375</v>
       </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1345,15 +1345,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>3932.995361328125</v>
       </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1388,15 +1388,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>3931.597412109375</v>
       </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1431,15 +1431,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
         <v>3931.305908203125</v>
       </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1474,15 +1474,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
         <v>3931.307861328125</v>
       </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1517,15 +1517,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>3932.846435546875</v>
       </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1560,15 +1560,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>3933.56689453125</v>
       </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1603,15 +1603,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>3933.525146484375</v>
       </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1646,15 +1646,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
         <v>3931.799072265625</v>
       </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1689,15 +1689,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
         <v>3930.87890625</v>
       </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1732,15 +1732,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
         <v>3931.912109375</v>
       </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1775,15 +1775,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
         <v>3932.565673828125</v>
       </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1818,15 +1818,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>3933.67236328125</v>
       </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1861,15 +1861,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>3933.635009765625</v>
       </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1904,15 +1904,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
         <v>3934.226318359375</v>
       </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1947,15 +1947,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
         <v>3935.292724609375</v>
       </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1990,15 +1990,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>3935.494384765625</v>
       </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2033,15 +2033,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>3934.62451171875</v>
       </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2076,15 +2076,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>3932.925537109375</v>
       </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2119,15 +2119,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
         <v>3931.341796875</v>
       </c>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2162,15 +2162,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
         <v>3930.907470703125</v>
       </c>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2205,15 +2205,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
         <v>3930.149658203125</v>
       </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2248,15 +2248,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
         <v>3929.44775390625</v>
       </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2291,15 +2291,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
         <v>3928.668701171875</v>
       </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2334,15 +2334,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
         <v>3927.259765625</v>
       </c>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2377,15 +2377,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>3927.22998046875</v>
       </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2420,15 +2420,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
         <v>3929.36865234375</v>
       </c>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2463,15 +2463,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
         <v>3929.566650390625</v>
       </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2506,15 +2506,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>3930.66357421875</v>
       </c>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2549,15 +2549,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
         <v>3931.087890625</v>
       </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2592,15 +2592,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
         <v>3932.123046875</v>
       </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2635,15 +2635,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
         <v>3931.64697265625</v>
       </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2678,15 +2678,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
         <v>3931.952392578125</v>
       </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2721,15 +2721,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
         <v>3931.818359375</v>
       </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2764,15 +2764,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
         <v>3931.340576171875</v>
       </c>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2807,15 +2807,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
         <v>3930.759765625</v>
       </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2850,15 +2850,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M56" t="n">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>3930.023681640625</v>
       </c>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2893,15 +2893,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
         <v>3929.658203125</v>
       </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2936,15 +2936,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
         <v>3930.375732421875</v>
       </c>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2979,15 +2979,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
         <v>3930.3671875</v>
       </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3022,15 +3022,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
         <v>3930.339599609375</v>
       </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3065,15 +3065,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
         <v>3932.077392578125</v>
       </c>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3108,15 +3108,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
         <v>3931.685302734375</v>
       </c>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3151,15 +3151,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
         <v>3931.225341796875</v>
       </c>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3194,15 +3194,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>3930.695068359375</v>
       </c>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3237,15 +3237,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
         <v>3930.54736328125</v>
       </c>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3280,15 +3280,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
         <v>3934.203125</v>
       </c>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3323,15 +3323,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
         <v>3936.5673828125</v>
       </c>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3366,15 +3366,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
         <v>3936.694580078125</v>
       </c>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3409,15 +3409,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
         <v>3935.03857421875</v>
       </c>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3452,15 +3452,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
         <v>3933.288330078125</v>
       </c>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3495,15 +3495,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
         <v>3932.96826171875</v>
       </c>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3538,15 +3538,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
         <v>3932.1083984375</v>
       </c>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3581,15 +3581,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
         <v>3932.264404296875</v>
       </c>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3624,15 +3624,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
         <v>3932.906005859375</v>
       </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3667,15 +3667,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
         <v>3933.141845703125</v>
       </c>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3710,15 +3710,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
         <v>3932.93310546875</v>
       </c>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3753,15 +3753,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
         <v>3931.939208984375</v>
       </c>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3796,15 +3796,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
         <v>3931.176025390625</v>
       </c>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3839,15 +3839,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
         <v>3931.567138671875</v>
       </c>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3882,15 +3882,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
         <v>3931.46044921875</v>
       </c>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3925,15 +3925,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
         <v>3932.093017578125</v>
       </c>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3968,15 +3968,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
         <v>3934.1015625</v>
       </c>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4011,15 +4011,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
         <v>3935.36865234375</v>
       </c>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4054,15 +4054,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
         <v>3932.9765625</v>
       </c>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4097,15 +4097,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
         <v>3930.559326171875</v>
       </c>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4140,15 +4140,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
         <v>3930.431884765625</v>
       </c>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4183,15 +4183,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
         <v>3931.35986328125</v>
       </c>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4226,15 +4226,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
         <v>3933.51171875</v>
       </c>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4269,15 +4269,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
         <v>3935.465576171875</v>
       </c>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4312,15 +4312,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
         <v>3936.763427734375</v>
       </c>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4355,15 +4355,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
         <v>3937.120361328125</v>
       </c>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4398,15 +4398,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
         <v>3937.867431640625</v>
       </c>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4441,15 +4441,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M93" t="n">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
         <v>3937.51220703125</v>
       </c>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4484,15 +4484,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M94" t="n">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
         <v>3936.51123046875</v>
       </c>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4527,15 +4527,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
         <v>3937.77978515625</v>
       </c>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4570,15 +4570,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M96" t="n">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
         <v>3944.0595703125</v>
       </c>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4613,15 +4613,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M97" t="n">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
         <v>3943.034912109375</v>
       </c>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4656,15 +4656,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M98" t="n">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
         <v>3931.768310546875</v>
       </c>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4699,15 +4699,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M99" t="n">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
         <v>3924.546630859375</v>
       </c>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4742,15 +4742,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
         <v>3926.761962890625</v>
       </c>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4785,15 +4785,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M101" t="n">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
         <v>3939.109619140625</v>
       </c>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4828,15 +4828,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M102" t="n">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
         <v>3958.180419921875</v>
       </c>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4871,15 +4871,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M103" t="n">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
         <v>3980.4130859375</v>
       </c>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4914,15 +4914,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M104" t="n">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
         <v>3993.5380859375</v>
       </c>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4957,15 +4957,15 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M105" t="n">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
         <v>4001.036865234375</v>
       </c>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5000,16 +5000,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K106" t="n">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>4001.498779296875</v>
+      </c>
+      <c r="M106" t="n">
         <v>3918.46385418379</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M106" t="n">
-        <v>4001.498779296875</v>
       </c>
     </row>
     <row r="107">
@@ -5045,16 +5045,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K107" t="n">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>4006.662841796875</v>
+      </c>
+      <c r="M107" t="n">
         <v>3900.5545482998</v>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
-        <v>4006.662841796875</v>
       </c>
     </row>
     <row r="108">
@@ -5090,16 +5090,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K108" t="n">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>4015.2021484375</v>
+      </c>
+      <c r="M108" t="n">
         <v>3880.30103467208</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M108" t="n">
-        <v>4015.2021484375</v>
       </c>
     </row>
     <row r="109">
@@ -5135,16 +5135,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K109" t="n">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>4019.144287109375</v>
+      </c>
+      <c r="M109" t="n">
         <v>3891.0598236152</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M109" t="n">
-        <v>4019.144287109375</v>
       </c>
     </row>
     <row r="110">
@@ -5180,16 +5180,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K110" t="n">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>4022.361083984375</v>
+      </c>
+      <c r="M110" t="n">
         <v>3891.69786568916</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M110" t="n">
-        <v>4022.361083984375</v>
       </c>
     </row>
     <row r="111">
@@ -5225,16 +5225,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K111" t="n">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>4048.4453125</v>
+      </c>
+      <c r="M111" t="n">
         <v>3890.9122918221</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M111" t="n">
-        <v>4048.4453125</v>
       </c>
     </row>
     <row r="112">
@@ -5270,16 +5270,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K112" t="n">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>4076.952392578125</v>
+      </c>
+      <c r="M112" t="n">
         <v>3859.50662602166</v>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M112" t="n">
-        <v>4076.952392578125</v>
       </c>
     </row>
     <row r="113">
@@ -5315,16 +5315,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K113" t="n">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>4065.91162109375</v>
+      </c>
+      <c r="M113" t="n">
         <v>3882.4682371953</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M113" t="n">
-        <v>4065.91162109375</v>
       </c>
     </row>
     <row r="114">
@@ -5360,16 +5360,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>3998.89404296875</v>
+      </c>
+      <c r="M114" t="n">
         <v>3901.93732954809</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M114" t="n">
-        <v>3998.89404296875</v>
       </c>
     </row>
     <row r="115">
@@ -5405,16 +5405,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K115" t="n">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>3971.868408203125</v>
+      </c>
+      <c r="M115" t="n">
         <v>3921.09159959239</v>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M115" t="n">
-        <v>3971.868408203125</v>
       </c>
     </row>
     <row r="116">
@@ -5450,16 +5450,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K116" t="n">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>3966.738037109375</v>
+      </c>
+      <c r="M116" t="n">
         <v>3925.35981291915</v>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M116" t="n">
-        <v>3966.738037109375</v>
       </c>
     </row>
     <row r="117">
@@ -5495,16 +5495,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K117" t="n">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>3946.650634765625</v>
+      </c>
+      <c r="M117" t="n">
         <v>3900.98578241379</v>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M117" t="n">
-        <v>3946.650634765625</v>
       </c>
     </row>
     <row r="118">
@@ -5540,16 +5540,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K118" t="n">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>3926.5205078125</v>
+      </c>
+      <c r="M118" t="n">
         <v>3893.41605124833</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
-        <v>3926.5205078125</v>
       </c>
     </row>
     <row r="119">
@@ -5585,16 +5585,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K119" t="n">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>3956.401123046875</v>
+      </c>
+      <c r="M119" t="n">
         <v>3891.14989045765</v>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M119" t="n">
-        <v>3956.401123046875</v>
       </c>
     </row>
     <row r="120">
@@ -5630,16 +5630,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K120" t="n">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>3952.32958984375</v>
+      </c>
+      <c r="M120" t="n">
         <v>3903.04431196441</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M120" t="n">
-        <v>3952.32958984375</v>
       </c>
     </row>
     <row r="121">
@@ -5675,16 +5675,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K121" t="n">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>3936.456787109375</v>
+      </c>
+      <c r="M121" t="n">
         <v>3894.69131211616</v>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M121" t="n">
-        <v>3936.456787109375</v>
       </c>
     </row>
     <row r="122">
@@ -5720,16 +5720,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K122" t="n">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>3944.68408203125</v>
+      </c>
+      <c r="M122" t="n">
         <v>3879.92627757264</v>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M122" t="n">
-        <v>3944.68408203125</v>
       </c>
     </row>
     <row r="123">
@@ -5765,16 +5765,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K123" t="n">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>3954.493408203125</v>
+      </c>
+      <c r="M123" t="n">
         <v>3870.54006120462</v>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M123" t="n">
-        <v>3954.493408203125</v>
       </c>
     </row>
     <row r="124">
@@ -5810,16 +5810,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K124" t="n">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>3973.6904296875</v>
+      </c>
+      <c r="M124" t="n">
         <v>3875.64489176435</v>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M124" t="n">
-        <v>3973.6904296875</v>
       </c>
     </row>
     <row r="125">
@@ -5855,16 +5855,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K125" t="n">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>3985.375732421875</v>
+      </c>
+      <c r="M125" t="n">
         <v>3900.16085575817</v>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>3985.375732421875</v>
       </c>
     </row>
     <row r="126">
@@ -5900,16 +5900,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K126" t="n">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>3981.828857421875</v>
+      </c>
+      <c r="M126" t="n">
         <v>3920.88792009678</v>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M126" t="n">
-        <v>3981.828857421875</v>
       </c>
     </row>
     <row r="127">
@@ -5945,16 +5945,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K127" t="n">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>3982.693359375</v>
+      </c>
+      <c r="M127" t="n">
         <v>3899.5857122835</v>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
-        <v>3982.693359375</v>
       </c>
     </row>
     <row r="128">
@@ -5990,16 +5990,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>3971.5439453125</v>
+      </c>
+      <c r="M128" t="n">
         <v>3905.14449948786</v>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M128" t="n">
-        <v>3971.5439453125</v>
       </c>
     </row>
     <row r="129">
@@ -6035,16 +6035,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K129" t="n">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>3911.2724609375</v>
+      </c>
+      <c r="M129" t="n">
         <v>3910.23319375772</v>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M129" t="n">
-        <v>3911.2724609375</v>
       </c>
     </row>
     <row r="130">
@@ -6080,16 +6080,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K130" t="n">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>3893.496826171875</v>
+      </c>
+      <c r="M130" t="n">
         <v>3918.95732827299</v>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M130" t="n">
-        <v>3893.496826171875</v>
       </c>
     </row>
     <row r="131">
@@ -6125,16 +6125,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K131" t="n">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>3897.945068359375</v>
+      </c>
+      <c r="M131" t="n">
         <v>3913.52779604362</v>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M131" t="n">
-        <v>3897.945068359375</v>
       </c>
     </row>
     <row r="132">
@@ -6170,16 +6170,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K132" t="n">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>3913.5244140625</v>
+      </c>
+      <c r="M132" t="n">
         <v>3898.92824079929</v>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M132" t="n">
-        <v>3913.5244140625</v>
       </c>
     </row>
     <row r="133">
@@ -6215,16 +6215,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K133" t="n">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>3913.530517578125</v>
+      </c>
+      <c r="M133" t="n">
         <v>3892.62405579653</v>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M133" t="n">
-        <v>3913.530517578125</v>
       </c>
     </row>
     <row r="134">
@@ -6260,16 +6260,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K134" t="n">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>3923.541259765625</v>
+      </c>
+      <c r="M134" t="n">
         <v>3893.65150935562</v>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M134" t="n">
-        <v>3923.541259765625</v>
       </c>
     </row>
     <row r="135">
@@ -6305,16 +6305,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>3927.414794921875</v>
+      </c>
+      <c r="M135" t="n">
         <v>3891.84292764198</v>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M135" t="n">
-        <v>3927.414794921875</v>
       </c>
     </row>
     <row r="136">
@@ -6350,16 +6350,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>3934.24365234375</v>
+      </c>
+      <c r="M136" t="n">
         <v>3893.2708246395</v>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M136" t="n">
-        <v>3934.24365234375</v>
       </c>
     </row>
     <row r="137">
@@ -6395,16 +6395,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K137" t="n">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>3949.395751953125</v>
+      </c>
+      <c r="M137" t="n">
         <v>3868.52006116247</v>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M137" t="n">
-        <v>3949.395751953125</v>
       </c>
     </row>
     <row r="138">
@@ -6440,16 +6440,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K138" t="n">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>3958.208984375</v>
+      </c>
+      <c r="M138" t="n">
         <v>3849.74104218566</v>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M138" t="n">
-        <v>3958.208984375</v>
       </c>
     </row>
     <row r="139">
@@ -6485,16 +6485,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>3945.195556640625</v>
+      </c>
+      <c r="M139" t="n">
         <v>3849.43099490173</v>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M139" t="n">
-        <v>3945.195556640625</v>
       </c>
     </row>
     <row r="140">
@@ -6530,16 +6530,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>3921.946044921875</v>
+      </c>
+      <c r="M140" t="n">
         <v>3853.76852841252</v>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M140" t="n">
-        <v>3921.946044921875</v>
       </c>
     </row>
     <row r="141">
@@ -6575,16 +6575,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K141" t="n">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>3904.229248046875</v>
+      </c>
+      <c r="M141" t="n">
         <v>3855.61168789017</v>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
-        <v>3904.229248046875</v>
       </c>
     </row>
     <row r="142">
@@ -6620,16 +6620,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>3901.041259765625</v>
+      </c>
+      <c r="M142" t="n">
         <v>3836.30362912404</v>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M142" t="n">
-        <v>3901.041259765625</v>
       </c>
     </row>
     <row r="143">
@@ -6665,16 +6665,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K143" t="n">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>3900.584716796875</v>
+      </c>
+      <c r="M143" t="n">
         <v>3826.1313449209</v>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M143" t="n">
-        <v>3900.584716796875</v>
       </c>
     </row>
     <row r="144">
@@ -6710,16 +6710,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K144" t="n">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>3903.847412109375</v>
+      </c>
+      <c r="M144" t="n">
         <v>3826.69364522608</v>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M144" t="n">
-        <v>3903.847412109375</v>
       </c>
     </row>
     <row r="145">
@@ -6755,16 +6755,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K145" t="n">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>3911.82470703125</v>
+      </c>
+      <c r="M145" t="n">
         <v>3834.76837640208</v>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M145" t="n">
-        <v>3911.82470703125</v>
       </c>
     </row>
     <row r="146">
@@ -6800,16 +6800,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K146" t="n">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>3922.0478515625</v>
+      </c>
+      <c r="M146" t="n">
         <v>3837.12723853151</v>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M146" t="n">
-        <v>3922.0478515625</v>
       </c>
     </row>
     <row r="147">
@@ -6845,16 +6845,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K147" t="n">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>3922.04638671875</v>
+      </c>
+      <c r="M147" t="n">
         <v>3818.44273210966</v>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M147" t="n">
-        <v>3922.04638671875</v>
       </c>
     </row>
     <row r="148">
@@ -6890,16 +6890,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K148" t="n">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>3919.676513671875</v>
+      </c>
+      <c r="M148" t="n">
         <v>3820.87881791205</v>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M148" t="n">
-        <v>3919.676513671875</v>
       </c>
     </row>
     <row r="149">
@@ -6935,16 +6935,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K149" t="n">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>3922.408203125</v>
+      </c>
+      <c r="M149" t="n">
         <v>3832.20731668121</v>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M149" t="n">
-        <v>3922.408203125</v>
       </c>
     </row>
     <row r="150">
@@ -6980,16 +6980,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K150" t="n">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>3929.969970703125</v>
+      </c>
+      <c r="M150" t="n">
         <v>3832.83910182644</v>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M150" t="n">
-        <v>3929.969970703125</v>
       </c>
     </row>
     <row r="151">
@@ -7025,16 +7025,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K151" t="n">
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>3941.244384765625</v>
+      </c>
+      <c r="M151" t="n">
         <v>3840.19889656757</v>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M151" t="n">
-        <v>3941.244384765625</v>
       </c>
     </row>
     <row r="152">
@@ -7070,16 +7070,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K152" t="n">
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>3950.422607421875</v>
+      </c>
+      <c r="M152" t="n">
         <v>3826.6195500175</v>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M152" t="n">
-        <v>3950.422607421875</v>
       </c>
     </row>
     <row r="153">
@@ -7115,16 +7115,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K153" t="n">
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>3957.150146484375</v>
+      </c>
+      <c r="M153" t="n">
         <v>3825.71147207223</v>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M153" t="n">
-        <v>3957.150146484375</v>
       </c>
     </row>
     <row r="154">
@@ -7160,16 +7160,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K154" t="n">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>3959.704345703125</v>
+      </c>
+      <c r="M154" t="n">
         <v>3839.51540943234</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M154" t="n">
-        <v>3959.704345703125</v>
       </c>
     </row>
     <row r="155">
@@ -7205,16 +7205,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K155" t="n">
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>3956.0107421875</v>
+      </c>
+      <c r="M155" t="n">
         <v>3850.2201912012</v>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M155" t="n">
-        <v>3956.0107421875</v>
       </c>
     </row>
     <row r="156">
@@ -7250,16 +7250,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K156" t="n">
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>3947.4033203125</v>
+      </c>
+      <c r="M156" t="n">
         <v>3854.51639605121</v>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M156" t="n">
-        <v>3947.4033203125</v>
       </c>
     </row>
     <row r="157">
@@ -7295,16 +7295,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K157" t="n">
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>3941.94873046875</v>
+      </c>
+      <c r="M157" t="n">
         <v>3843.0685216682</v>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M157" t="n">
-        <v>3941.94873046875</v>
       </c>
     </row>
     <row r="158">
@@ -7340,16 +7340,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K158" t="n">
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>3937.927001953125</v>
+      </c>
+      <c r="M158" t="n">
         <v>3839.15135497414</v>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M158" t="n">
-        <v>3937.927001953125</v>
       </c>
     </row>
     <row r="159">
@@ -7385,16 +7385,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K159" t="n">
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>3935.24853515625</v>
+      </c>
+      <c r="M159" t="n">
         <v>3848.35546178505</v>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M159" t="n">
-        <v>3935.24853515625</v>
       </c>
     </row>
     <row r="160">
@@ -7430,16 +7430,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K160" t="n">
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>3935.59033203125</v>
+      </c>
+      <c r="M160" t="n">
         <v>3849.09904836725</v>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M160" t="n">
-        <v>3935.59033203125</v>
       </c>
     </row>
     <row r="161">
@@ -7475,16 +7475,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K161" t="n">
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>3938.045654296875</v>
+      </c>
+      <c r="M161" t="n">
         <v>3853.75831973933</v>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M161" t="n">
-        <v>3938.045654296875</v>
       </c>
     </row>
     <row r="162">
@@ -7520,16 +7520,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K162" t="n">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>3943.2861328125</v>
+      </c>
+      <c r="M162" t="n">
         <v>3843.52214900079</v>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M162" t="n">
-        <v>3943.2861328125</v>
       </c>
     </row>
     <row r="163">
@@ -7565,16 +7565,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K163" t="n">
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>3952.003173828125</v>
+      </c>
+      <c r="M163" t="n">
         <v>3841.49770324612</v>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M163" t="n">
-        <v>3952.003173828125</v>
       </c>
     </row>
     <row r="164">
@@ -7610,16 +7610,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K164" t="n">
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>3959.649169921875</v>
+      </c>
+      <c r="M164" t="n">
         <v>3848.37703172355</v>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M164" t="n">
-        <v>3959.649169921875</v>
       </c>
     </row>
     <row r="165">
@@ -7655,16 +7655,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K165" t="n">
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>3960.87451171875</v>
+      </c>
+      <c r="M165" t="n">
         <v>3851.91433698158</v>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M165" t="n">
-        <v>3960.87451171875</v>
       </c>
     </row>
     <row r="166">
@@ -7700,16 +7700,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K166" t="n">
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>3958.702392578125</v>
+      </c>
+      <c r="M166" t="n">
         <v>3861.39424262446</v>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M166" t="n">
-        <v>3958.702392578125</v>
       </c>
     </row>
     <row r="167">
@@ -7745,16 +7745,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K167" t="n">
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>3958.72119140625</v>
+      </c>
+      <c r="M167" t="n">
         <v>3848.98411846592</v>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M167" t="n">
-        <v>3958.72119140625</v>
       </c>
     </row>
     <row r="168">
@@ -7790,16 +7790,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K168" t="n">
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>3957.050048828125</v>
+      </c>
+      <c r="M168" t="n">
         <v>3841.76296409287</v>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M168" t="n">
-        <v>3957.050048828125</v>
       </c>
     </row>
     <row r="169">
@@ -7835,16 +7835,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K169" t="n">
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>3954.96533203125</v>
+      </c>
+      <c r="M169" t="n">
         <v>3857.34831492347</v>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M169" t="n">
-        <v>3954.96533203125</v>
       </c>
     </row>
     <row r="170">
@@ -7880,16 +7880,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K170" t="n">
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>3953.236083984375</v>
+      </c>
+      <c r="M170" t="n">
         <v>3852.5563308</v>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M170" t="n">
-        <v>3953.236083984375</v>
       </c>
     </row>
     <row r="171">
@@ -7925,16 +7925,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K171" t="n">
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>3951.034912109375</v>
+      </c>
+      <c r="M171" t="n">
         <v>3861.66855955226</v>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M171" t="n">
-        <v>3951.034912109375</v>
       </c>
     </row>
     <row r="172">
@@ -7970,16 +7970,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K172" t="n">
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>3947.57763671875</v>
+      </c>
+      <c r="M172" t="n">
         <v>3849.40646115488</v>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M172" t="n">
-        <v>3947.57763671875</v>
       </c>
     </row>
     <row r="173">
@@ -8015,16 +8015,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K173" t="n">
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>3944.95556640625</v>
+      </c>
+      <c r="M173" t="n">
         <v>3848.4335087381</v>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M173" t="n">
-        <v>3944.95556640625</v>
       </c>
     </row>
     <row r="174">
@@ -8060,16 +8060,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K174" t="n">
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>3942.405517578125</v>
+      </c>
+      <c r="M174" t="n">
         <v>3849.27885274009</v>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M174" t="n">
-        <v>3942.405517578125</v>
       </c>
     </row>
     <row r="175">
@@ -8105,16 +8105,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K175" t="n">
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>3941.078125</v>
+      </c>
+      <c r="M175" t="n">
         <v>3859.76694718783</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M175" t="n">
-        <v>3941.078125</v>
       </c>
     </row>
     <row r="176">
@@ -8150,16 +8150,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K176" t="n">
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>3941.247314453125</v>
+      </c>
+      <c r="M176" t="n">
         <v>3861.22415295675</v>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M176" t="n">
-        <v>3941.247314453125</v>
       </c>
     </row>
     <row r="177">
@@ -8195,16 +8195,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K177" t="n">
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>3940.679931640625</v>
+      </c>
+      <c r="M177" t="n">
         <v>3851.54633077893</v>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M177" t="n">
-        <v>3940.679931640625</v>
       </c>
     </row>
     <row r="178">
@@ -8240,16 +8240,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K178" t="n">
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>3938.271484375</v>
+      </c>
+      <c r="M178" t="n">
         <v>3849.93681819236</v>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M178" t="n">
-        <v>3938.271484375</v>
       </c>
     </row>
     <row r="179">
@@ -8285,16 +8285,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K179" t="n">
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>3936.432373046875</v>
+      </c>
+      <c r="M179" t="n">
         <v>3854.6940598958</v>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M179" t="n">
-        <v>3936.432373046875</v>
       </c>
     </row>
     <row r="180">
@@ -8330,16 +8330,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K180" t="n">
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>3936.564697265625</v>
+      </c>
+      <c r="M180" t="n">
         <v>3855.55537553164</v>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M180" t="n">
-        <v>3936.564697265625</v>
       </c>
     </row>
     <row r="181">
@@ -8375,16 +8375,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K181" t="n">
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>3938.22802734375</v>
+      </c>
+      <c r="M181" t="n">
         <v>3862.31351717903</v>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M181" t="n">
-        <v>3938.22802734375</v>
       </c>
     </row>
     <row r="182">
@@ -8420,16 +8420,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K182" t="n">
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>3940.048583984375</v>
+      </c>
+      <c r="M182" t="n">
         <v>3852.67603572588</v>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M182" t="n">
-        <v>3940.048583984375</v>
       </c>
     </row>
     <row r="183">
@@ -8465,16 +8465,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K183" t="n">
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>3942.4326171875</v>
+      </c>
+      <c r="M183" t="n">
         <v>3846.34616438414</v>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M183" t="n">
-        <v>3942.4326171875</v>
       </c>
     </row>
     <row r="184">
@@ -8510,16 +8510,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K184" t="n">
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>3941.7373046875</v>
+      </c>
+      <c r="M184" t="n">
         <v>3855.48457344344</v>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M184" t="n">
-        <v>3941.7373046875</v>
       </c>
     </row>
     <row r="185">
@@ -8555,16 +8555,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K185" t="n">
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>3940.098876953125</v>
+      </c>
+      <c r="M185" t="n">
         <v>3861.42684451624</v>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M185" t="n">
-        <v>3940.098876953125</v>
       </c>
     </row>
     <row r="186">
@@ -8600,16 +8600,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K186" t="n">
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>3939.356201171875</v>
+      </c>
+      <c r="M186" t="n">
         <v>3864.32363786003</v>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M186" t="n">
-        <v>3939.356201171875</v>
       </c>
     </row>
     <row r="187">
@@ -8645,16 +8645,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K187" t="n">
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>3939.001220703125</v>
+      </c>
+      <c r="M187" t="n">
         <v>3856.59929469265</v>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M187" t="n">
-        <v>3939.001220703125</v>
       </c>
     </row>
     <row r="188">
@@ -8690,16 +8690,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K188" t="n">
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>3939.409912109375</v>
+      </c>
+      <c r="M188" t="n">
         <v>3851.20384625923</v>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M188" t="n">
-        <v>3939.409912109375</v>
       </c>
     </row>
     <row r="189">
@@ -8735,16 +8735,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K189" t="n">
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>3936.661865234375</v>
+      </c>
+      <c r="M189" t="n">
         <v>3862.822304278</v>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M189" t="n">
-        <v>3936.661865234375</v>
       </c>
     </row>
     <row r="190">
@@ -8780,16 +8780,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K190" t="n">
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>3932.85693359375</v>
+      </c>
+      <c r="M190" t="n">
         <v>3863.34146470618</v>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M190" t="n">
-        <v>3932.85693359375</v>
       </c>
     </row>
     <row r="191">
@@ -8825,16 +8825,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K191" t="n">
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>3927.611328125</v>
+      </c>
+      <c r="M191" t="n">
         <v>3870.23561222533</v>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M191" t="n">
-        <v>3927.611328125</v>
       </c>
     </row>
     <row r="192">
@@ -8870,16 +8870,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K192" t="n">
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>3923.406005859375</v>
+      </c>
+      <c r="M192" t="n">
         <v>3859.73632116829</v>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M192" t="n">
-        <v>3923.406005859375</v>
       </c>
     </row>
     <row r="193">
@@ -8915,16 +8915,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K193" t="n">
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>3921.287353515625</v>
+      </c>
+      <c r="M193" t="n">
         <v>3856.44254216248</v>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M193" t="n">
-        <v>3921.287353515625</v>
       </c>
     </row>
     <row r="194">
@@ -8960,16 +8960,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K194" t="n">
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>3919.112060546875</v>
+      </c>
+      <c r="M194" t="n">
         <v>3860.64884482606</v>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M194" t="n">
-        <v>3919.112060546875</v>
       </c>
     </row>
     <row r="195">
@@ -9005,16 +9005,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K195" t="n">
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>3914.9658203125</v>
+      </c>
+      <c r="M195" t="n">
         <v>3865.89280972192</v>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M195" t="n">
-        <v>3914.9658203125</v>
       </c>
     </row>
     <row r="196">
@@ -9050,16 +9050,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K196" t="n">
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>3912.291015625</v>
+      </c>
+      <c r="M196" t="n">
         <v>3867.53574748037</v>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M196" t="n">
-        <v>3912.291015625</v>
       </c>
     </row>
     <row r="197">
@@ -9095,16 +9095,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K197" t="n">
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>3910.81494140625</v>
+      </c>
+      <c r="M197" t="n">
         <v>3860.06365733423</v>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M197" t="n">
-        <v>3910.81494140625</v>
       </c>
     </row>
     <row r="198">
@@ -9140,16 +9140,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K198" t="n">
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>3910.78125</v>
+      </c>
+      <c r="M198" t="n">
         <v>3854.15415280922</v>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M198" t="n">
-        <v>3910.78125</v>
       </c>
     </row>
     <row r="199">
@@ -9185,16 +9185,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K199" t="n">
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>3911.770263671875</v>
+      </c>
+      <c r="M199" t="n">
         <v>3859.34180534655</v>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M199" t="n">
-        <v>3911.770263671875</v>
       </c>
     </row>
     <row r="200">
@@ -9230,16 +9230,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K200" t="n">
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>3915.401611328125</v>
+      </c>
+      <c r="M200" t="n">
         <v>3866.84518013632</v>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M200" t="n">
-        <v>3915.401611328125</v>
       </c>
     </row>
     <row r="201">
@@ -9275,16 +9275,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K201" t="n">
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>3922.068115234375</v>
+      </c>
+      <c r="M201" t="n">
         <v>3864.80624465197</v>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M201" t="n">
-        <v>3922.068115234375</v>
       </c>
     </row>
     <row r="202">
@@ -9320,16 +9320,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K202" t="n">
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>3932.35205078125</v>
+      </c>
+      <c r="M202" t="n">
         <v>3862.28239719142</v>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M202" t="n">
-        <v>3932.35205078125</v>
       </c>
     </row>
     <row r="203">
@@ -9365,16 +9365,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K203" t="n">
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>3943.21435546875</v>
+      </c>
+      <c r="M203" t="n">
         <v>3863.47088433719</v>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M203" t="n">
-        <v>3943.21435546875</v>
       </c>
     </row>
     <row r="204">
@@ -9410,16 +9410,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K204" t="n">
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>3957.739013671875</v>
+      </c>
+      <c r="M204" t="n">
         <v>3867.20429491395</v>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M204" t="n">
-        <v>3957.739013671875</v>
       </c>
     </row>
     <row r="205">
@@ -9455,16 +9455,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K205" t="n">
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>3975.099365234375</v>
+      </c>
+      <c r="M205" t="n">
         <v>3870.81207294815</v>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M205" t="n">
-        <v>3975.099365234375</v>
       </c>
     </row>
     <row r="206">
@@ -9500,16 +9500,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K206" t="n">
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>3995.761962890625</v>
+      </c>
+      <c r="M206" t="n">
         <v>3879.64257525175</v>
-      </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M206" t="n">
-        <v>3995.761962890625</v>
       </c>
     </row>
     <row r="207">
@@ -9545,16 +9545,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K207" t="n">
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>4019.4453125</v>
+      </c>
+      <c r="M207" t="n">
         <v>3869.80701260765</v>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M207" t="n">
-        <v>4019.4453125</v>
       </c>
     </row>
     <row r="208">
@@ -9590,16 +9590,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K208" t="n">
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>4036.74853515625</v>
+      </c>
+      <c r="M208" t="n">
         <v>3864.98637833685</v>
-      </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M208" t="n">
-        <v>4036.74853515625</v>
       </c>
     </row>
     <row r="209">
@@ -9635,16 +9635,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K209" t="n">
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>4045.140380859375</v>
+      </c>
+      <c r="M209" t="n">
         <v>3874.82786859765</v>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M209" t="n">
-        <v>4045.140380859375</v>
       </c>
     </row>
     <row r="210">
@@ -9680,16 +9680,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K210" t="n">
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>4045.7197265625</v>
+      </c>
+      <c r="M210" t="n">
         <v>3884.17621408128</v>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M210" t="n">
-        <v>4045.7197265625</v>
       </c>
     </row>
     <row r="211">
@@ -9725,16 +9725,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K211" t="n">
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>4043.469970703125</v>
+      </c>
+      <c r="M211" t="n">
         <v>3912.01641844443</v>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M211" t="n">
-        <v>4043.469970703125</v>
       </c>
     </row>
     <row r="212">
@@ -9770,16 +9770,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K212" t="n">
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>4049.938232421875</v>
+      </c>
+      <c r="M212" t="n">
         <v>3892.29639031854</v>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M212" t="n">
-        <v>4049.938232421875</v>
       </c>
     </row>
     <row r="213">
@@ -9815,16 +9815,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K213" t="n">
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>4062.82666015625</v>
+      </c>
+      <c r="M213" t="n">
         <v>3910.95521040141</v>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M213" t="n">
-        <v>4062.82666015625</v>
       </c>
     </row>
     <row r="214">
@@ -9860,16 +9860,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K214" t="n">
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>4079.6044921875</v>
+      </c>
+      <c r="M214" t="n">
         <v>3922.06817444159</v>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M214" t="n">
-        <v>4079.6044921875</v>
       </c>
     </row>
     <row r="215">
@@ -9905,16 +9905,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K215" t="n">
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>4096.8271484375</v>
+      </c>
+      <c r="M215" t="n">
         <v>3938.78339487517</v>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M215" t="n">
-        <v>4096.8271484375</v>
       </c>
     </row>
     <row r="216">
@@ -9950,16 +9950,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K216" t="n">
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>4106.9365234375</v>
+      </c>
+      <c r="M216" t="n">
         <v>3940.0319814679</v>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M216" t="n">
-        <v>4106.9365234375</v>
       </c>
     </row>
     <row r="217">
@@ -9995,16 +9995,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K217" t="n">
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>4092.280517578125</v>
+      </c>
+      <c r="M217" t="n">
         <v>3937.96011477974</v>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M217" t="n">
-        <v>4092.280517578125</v>
       </c>
     </row>
     <row r="218">
@@ -10040,16 +10040,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K218" t="n">
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>4062.991455078125</v>
+      </c>
+      <c r="M218" t="n">
         <v>3926.83677741035</v>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M218" t="n">
-        <v>4062.991455078125</v>
       </c>
     </row>
     <row r="219">
@@ -10085,16 +10085,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K219" t="n">
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>4132.1083984375</v>
+      </c>
+      <c r="M219" t="n">
         <v>3938.93603100486</v>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M219" t="n">
-        <v>4132.1083984375</v>
       </c>
     </row>
     <row r="220">
@@ -10130,16 +10130,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K220" t="n">
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>4188.6279296875</v>
+      </c>
+      <c r="M220" t="n">
         <v>3939.23043596699</v>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M220" t="n">
-        <v>4188.6279296875</v>
       </c>
     </row>
     <row r="221">
@@ -10175,16 +10175,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K221" t="n">
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>4187.5029296875</v>
+      </c>
+      <c r="M221" t="n">
         <v>3945.99779835144</v>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M221" t="n">
-        <v>4187.5029296875</v>
       </c>
     </row>
     <row r="222">
@@ -10220,16 +10220,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K222" t="n">
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>4171.2607421875</v>
+      </c>
+      <c r="M222" t="n">
         <v>3931.2187680463</v>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M222" t="n">
-        <v>4171.2607421875</v>
       </c>
     </row>
     <row r="223">
@@ -10265,16 +10265,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K223" t="n">
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>4150.7470703125</v>
+      </c>
+      <c r="M223" t="n">
         <v>3942.5268494691</v>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M223" t="n">
-        <v>4150.7470703125</v>
       </c>
     </row>
     <row r="224">
@@ -10310,16 +10310,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K224" t="n">
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>4127.119140625</v>
+      </c>
+      <c r="M224" t="n">
         <v>3937.03425398441</v>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M224" t="n">
-        <v>4127.119140625</v>
       </c>
     </row>
     <row r="225">
@@ -10355,16 +10355,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K225" t="n">
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>4108.9912109375</v>
+      </c>
+      <c r="M225" t="n">
         <v>3952.51784739522</v>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M225" t="n">
-        <v>4108.9912109375</v>
       </c>
     </row>
     <row r="226">
@@ -10400,16 +10400,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K226" t="n">
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>4093.509765625</v>
+      </c>
+      <c r="M226" t="n">
         <v>3957.2727839144</v>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M226" t="n">
-        <v>4093.509765625</v>
       </c>
     </row>
     <row r="227">
@@ -10445,16 +10445,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K227" t="n">
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>4081.798095703125</v>
+      </c>
+      <c r="M227" t="n">
         <v>3946.99660176322</v>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M227" t="n">
-        <v>4081.798095703125</v>
       </c>
     </row>
     <row r="228">
@@ -10490,16 +10490,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K228" t="n">
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>4077.849609375</v>
+      </c>
+      <c r="M228" t="n">
         <v>3936.94204661372</v>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M228" t="n">
-        <v>4077.849609375</v>
       </c>
     </row>
     <row r="229">
@@ -10535,16 +10535,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K229" t="n">
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>4075.23046875</v>
+      </c>
+      <c r="M229" t="n">
         <v>3947.51510356732</v>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M229" t="n">
-        <v>4075.23046875</v>
       </c>
     </row>
     <row r="230">
@@ -10580,16 +10580,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K230" t="n">
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>4078.42529296875</v>
+      </c>
+      <c r="M230" t="n">
         <v>3950.80624807682</v>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M230" t="n">
-        <v>4078.42529296875</v>
       </c>
     </row>
     <row r="231">
@@ -10625,16 +10625,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K231" t="n">
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>4082.189208984375</v>
+      </c>
+      <c r="M231" t="n">
         <v>3957.05560262522</v>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M231" t="n">
-        <v>4082.189208984375</v>
       </c>
     </row>
     <row r="232">
@@ -10670,16 +10670,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K232" t="n">
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>4098.79296875</v>
+      </c>
+      <c r="M232" t="n">
         <v>3942.82076046317</v>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M232" t="n">
-        <v>4098.79296875</v>
       </c>
     </row>
     <row r="233">
@@ -10715,16 +10715,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K233" t="n">
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>4115.92578125</v>
+      </c>
+      <c r="M233" t="n">
         <v>3949.56177788456</v>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M233" t="n">
-        <v>4115.92578125</v>
       </c>
     </row>
     <row r="234">
@@ -10760,16 +10760,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K234" t="n">
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>4124.3369140625</v>
+      </c>
+      <c r="M234" t="n">
         <v>3954.14761267214</v>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M234" t="n">
-        <v>4124.3369140625</v>
       </c>
     </row>
     <row r="235">
@@ -10805,16 +10805,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K235" t="n">
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>4131.6953125</v>
+      </c>
+      <c r="M235" t="n">
         <v>3963.94513977584</v>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M235" t="n">
-        <v>4131.6953125</v>
       </c>
     </row>
     <row r="236">
@@ -10850,16 +10850,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K236" t="n">
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>4134.70947265625</v>
+      </c>
+      <c r="M236" t="n">
         <v>3967.98662176431</v>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M236" t="n">
-        <v>4134.70947265625</v>
       </c>
     </row>
     <row r="237">
@@ -10895,16 +10895,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K237" t="n">
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>4134.7275390625</v>
+      </c>
+      <c r="M237" t="n">
         <v>3961.32645044829</v>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M237" t="n">
-        <v>4134.7275390625</v>
       </c>
     </row>
     <row r="238">
@@ -10940,16 +10940,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K238" t="n">
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>4130.572265625</v>
+      </c>
+      <c r="M238" t="n">
         <v>3959.21687753175</v>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M238" t="n">
-        <v>4130.572265625</v>
       </c>
     </row>
     <row r="239">
@@ -10985,16 +10985,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K239" t="n">
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>4123.9775390625</v>
+      </c>
+      <c r="M239" t="n">
         <v>3968.24134462584</v>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M239" t="n">
-        <v>4123.9775390625</v>
       </c>
     </row>
     <row r="240">
@@ -11030,16 +11030,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K240" t="n">
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>4116.80126953125</v>
+      </c>
+      <c r="M240" t="n">
         <v>3965.56403775549</v>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M240" t="n">
-        <v>4116.80126953125</v>
       </c>
     </row>
     <row r="241">
@@ -11075,16 +11075,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K241" t="n">
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>4110.4384765625</v>
+      </c>
+      <c r="M241" t="n">
         <v>3978.02767512024</v>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M241" t="n">
-        <v>4110.4384765625</v>
       </c>
     </row>
     <row r="242">
@@ -11120,16 +11120,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K242" t="n">
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>4106.5087890625</v>
+      </c>
+      <c r="M242" t="n">
         <v>3962.58047068965</v>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M242" t="n">
-        <v>4106.5087890625</v>
       </c>
     </row>
     <row r="243">
@@ -11165,16 +11165,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K243" t="n">
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>4105.5986328125</v>
+      </c>
+      <c r="M243" t="n">
         <v>3961.70861706859</v>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M243" t="n">
-        <v>4105.5986328125</v>
       </c>
     </row>
     <row r="244">
@@ -11210,16 +11210,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K244" t="n">
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>4109.541015625</v>
+      </c>
+      <c r="M244" t="n">
         <v>3968.26143266017</v>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M244" t="n">
-        <v>4109.541015625</v>
       </c>
     </row>
     <row r="245">
@@ -11255,16 +11255,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K245" t="n">
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>4114.68359375</v>
+      </c>
+      <c r="M245" t="n">
         <v>3974.721546913</v>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M245" t="n">
-        <v>4114.68359375</v>
       </c>
     </row>
     <row r="246">
@@ -11300,16 +11300,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K246" t="n">
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>4114.31640625</v>
+      </c>
+      <c r="M246" t="n">
         <v>3976.08703927929</v>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M246" t="n">
-        <v>4114.31640625</v>
       </c>
     </row>
     <row r="247">
@@ -11345,16 +11345,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K247" t="n">
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>4116.294921875</v>
+      </c>
+      <c r="M247" t="n">
         <v>3970.04185819455</v>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M247" t="n">
-        <v>4116.294921875</v>
       </c>
     </row>
     <row r="248">
@@ -11390,16 +11390,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K248" t="n">
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>4117.71435546875</v>
+      </c>
+      <c r="M248" t="n">
         <v>3966.48018384569</v>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M248" t="n">
-        <v>4117.71435546875</v>
       </c>
     </row>
     <row r="249">
@@ -11435,16 +11435,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K249" t="n">
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>4121.388671875</v>
+      </c>
+      <c r="M249" t="n">
         <v>3982.15428427058</v>
-      </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M249" t="n">
-        <v>4121.388671875</v>
       </c>
     </row>
     <row r="250">
@@ -11480,16 +11480,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K250" t="n">
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>4126.16064453125</v>
+      </c>
+      <c r="M250" t="n">
         <v>3987.06597331993</v>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M250" t="n">
-        <v>4126.16064453125</v>
       </c>
     </row>
     <row r="251">
@@ -11525,16 +11525,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K251" t="n">
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>4128.7431640625</v>
+      </c>
+      <c r="M251" t="n">
         <v>3996.60449650561</v>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M251" t="n">
-        <v>4128.7431640625</v>
       </c>
     </row>
     <row r="252">
@@ -11570,16 +11570,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K252" t="n">
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>4134.2626953125</v>
+      </c>
+      <c r="M252" t="n">
         <v>3975.49345433048</v>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M252" t="n">
-        <v>4134.2626953125</v>
       </c>
     </row>
     <row r="253">
@@ -11615,16 +11615,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K253" t="n">
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>4134.576171875</v>
+      </c>
+      <c r="M253" t="n">
         <v>3976.57853749626</v>
-      </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M253" t="n">
-        <v>4134.576171875</v>
       </c>
     </row>
     <row r="254">
@@ -11660,16 +11660,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K254" t="n">
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>4136.91552734375</v>
+      </c>
+      <c r="M254" t="n">
         <v>3977.3743200365</v>
-      </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M254" t="n">
-        <v>4136.91552734375</v>
       </c>
     </row>
     <row r="255">
@@ -11705,16 +11705,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K255" t="n">
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>4132.81640625</v>
+      </c>
+      <c r="M255" t="n">
         <v>3990.38280416841</v>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M255" t="n">
-        <v>4132.81640625</v>
       </c>
     </row>
     <row r="256">
@@ -11750,16 +11750,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K256" t="n">
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
+        <v>4130.4716796875</v>
+      </c>
+      <c r="M256" t="n">
         <v>3992.22382311781</v>
-      </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M256" t="n">
-        <v>4130.4716796875</v>
       </c>
     </row>
     <row r="257">
@@ -11795,16 +11795,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K257" t="n">
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>4125.4453125</v>
+      </c>
+      <c r="M257" t="n">
         <v>3979.54366308797</v>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M257" t="n">
-        <v>4125.4453125</v>
       </c>
     </row>
     <row r="258">
@@ -11840,16 +11840,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K258" t="n">
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>4122.5390625</v>
+      </c>
+      <c r="M258" t="n">
         <v>3976.04752183471</v>
-      </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M258" t="n">
-        <v>4122.5390625</v>
       </c>
     </row>
     <row r="259">
@@ -11885,16 +11885,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K259" t="n">
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
+        <v>4116.08349609375</v>
+      </c>
+      <c r="M259" t="n">
         <v>3997.54122459819</v>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M259" t="n">
-        <v>4116.08349609375</v>
       </c>
     </row>
     <row r="260">
@@ -11930,16 +11930,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K260" t="n">
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
+        <v>4110.759765625</v>
+      </c>
+      <c r="M260" t="n">
         <v>4000.14443625994</v>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>4110.759765625</v>
       </c>
     </row>
     <row r="261">
@@ -11975,16 +11975,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K261" t="n">
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
+        <v>4110.06640625</v>
+      </c>
+      <c r="M261" t="n">
         <v>4011.76124771853</v>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M261" t="n">
-        <v>4110.06640625</v>
       </c>
     </row>
     <row r="262">
@@ -12020,16 +12020,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K262" t="n">
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L262" t="n">
+        <v>4113.4638671875</v>
+      </c>
+      <c r="M262" t="n">
         <v>3988.44793128812</v>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M262" t="n">
-        <v>4113.4638671875</v>
       </c>
     </row>
     <row r="263">
@@ -12065,16 +12065,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K263" t="n">
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>4113.908203125</v>
+      </c>
+      <c r="M263" t="n">
         <v>3988.73542069745</v>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M263" t="n">
-        <v>4113.908203125</v>
       </c>
     </row>
     <row r="264">
@@ -12110,16 +12110,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K264" t="n">
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>4121.828125</v>
+      </c>
+      <c r="M264" t="n">
         <v>3999.51759079528</v>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M264" t="n">
-        <v>4121.828125</v>
       </c>
     </row>
     <row r="265">
@@ -12155,16 +12155,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K265" t="n">
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>4118.158203125</v>
+      </c>
+      <c r="M265" t="n">
         <v>4011.81690145298</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M265" t="n">
-        <v>4118.158203125</v>
       </c>
     </row>
     <row r="266">
@@ -12200,16 +12200,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K266" t="n">
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>4123.73095703125</v>
+      </c>
+      <c r="M266" t="n">
         <v>4014.5638578194</v>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M266" t="n">
-        <v>4123.73095703125</v>
       </c>
     </row>
     <row r="267">
@@ -12245,16 +12245,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K267" t="n">
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>4124.8056640625</v>
+      </c>
+      <c r="M267" t="n">
         <v>4006.4321556608</v>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M267" t="n">
-        <v>4124.8056640625</v>
       </c>
     </row>
     <row r="268">
@@ -12290,16 +12290,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K268" t="n">
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>4127.0751953125</v>
+      </c>
+      <c r="M268" t="n">
         <v>4005.91941681736</v>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M268" t="n">
-        <v>4127.0751953125</v>
       </c>
     </row>
     <row r="269">
@@ -12335,16 +12335,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K269" t="n">
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
+        <v>4129.23046875</v>
+      </c>
+      <c r="M269" t="n">
         <v>4011.02704652942</v>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M269" t="n">
-        <v>4129.23046875</v>
       </c>
     </row>
     <row r="270">
@@ -12380,16 +12380,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K270" t="n">
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>4126.712890625</v>
+      </c>
+      <c r="M270" t="n">
         <v>4011.53599828442</v>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M270" t="n">
-        <v>4126.712890625</v>
       </c>
     </row>
     <row r="271">
@@ -12425,16 +12425,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K271" t="n">
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>4129.818359375</v>
+      </c>
+      <c r="M271" t="n">
         <v>4020.99268742861</v>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M271" t="n">
-        <v>4129.818359375</v>
       </c>
     </row>
     <row r="272">
@@ -12470,16 +12470,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K272" t="n">
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
+        <v>4127.85546875</v>
+      </c>
+      <c r="M272" t="n">
         <v>4007.20752085467</v>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M272" t="n">
-        <v>4127.85546875</v>
       </c>
     </row>
     <row r="273">
@@ -12515,16 +12515,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K273" t="n">
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
+        <v>4126.9443359375</v>
+      </c>
+      <c r="M273" t="n">
         <v>4012.2165216113</v>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M273" t="n">
-        <v>4126.9443359375</v>
       </c>
     </row>
     <row r="274">
@@ -12560,16 +12560,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K274" t="n">
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L274" t="n">
+        <v>4119.87060546875</v>
+      </c>
+      <c r="M274" t="n">
         <v>4010.82419031391</v>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M274" t="n">
-        <v>4119.87060546875</v>
       </c>
     </row>
     <row r="275">
@@ -12605,16 +12605,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K275" t="n">
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>4114.7939453125</v>
+      </c>
+      <c r="M275" t="n">
         <v>4022.59544911839</v>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M275" t="n">
-        <v>4114.7939453125</v>
       </c>
     </row>
     <row r="276">
@@ -12650,16 +12650,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K276" t="n">
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L276" t="n">
+        <v>4114.978515625</v>
+      </c>
+      <c r="M276" t="n">
         <v>4022.22299720322</v>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M276" t="n">
-        <v>4114.978515625</v>
       </c>
     </row>
     <row r="277">
@@ -12695,16 +12695,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K277" t="n">
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>4120.263671875</v>
+      </c>
+      <c r="M277" t="n">
         <v>4017.83936000708</v>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M277" t="n">
-        <v>4120.263671875</v>
       </c>
     </row>
     <row r="278">
@@ -12740,16 +12740,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K278" t="n">
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>4120.5595703125</v>
+      </c>
+      <c r="M278" t="n">
         <v>4013.11965987599</v>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M278" t="n">
-        <v>4120.5595703125</v>
       </c>
     </row>
     <row r="279">
@@ -12785,16 +12785,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K279" t="n">
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>4115.1533203125</v>
+      </c>
+      <c r="M279" t="n">
         <v>4022.53979538394</v>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M279" t="n">
-        <v>4115.1533203125</v>
       </c>
     </row>
     <row r="280">
@@ -12830,16 +12830,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K280" t="n">
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>4110.7646484375</v>
+      </c>
+      <c r="M280" t="n">
         <v>4024.8212691844</v>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M280" t="n">
-        <v>4110.7646484375</v>
       </c>
     </row>
     <row r="281">
@@ -12875,16 +12875,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K281" t="n">
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>4111.13623046875</v>
+      </c>
+      <c r="M281" t="n">
         <v>4030.9705128732</v>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M281" t="n">
-        <v>4111.13623046875</v>
       </c>
     </row>
     <row r="282">
@@ -12920,16 +12920,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K282" t="n">
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>4110.59423828125</v>
+      </c>
+      <c r="M282" t="n">
         <v>4018.5900267981</v>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M282" t="n">
-        <v>4110.59423828125</v>
       </c>
     </row>
     <row r="283">
@@ -12965,16 +12965,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K283" t="n">
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>4116.93310546875</v>
+      </c>
+      <c r="M283" t="n">
         <v>4019.88125929977</v>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M283" t="n">
-        <v>4116.93310546875</v>
       </c>
     </row>
     <row r="284">
@@ -13010,16 +13010,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K284" t="n">
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>4122.884765625</v>
+      </c>
+      <c r="M284" t="n">
         <v>4025.37912377707</v>
-      </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M284" t="n">
-        <v>4122.884765625</v>
       </c>
     </row>
     <row r="285">
@@ -13055,16 +13055,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K285" t="n">
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>4131.3505859375</v>
+      </c>
+      <c r="M285" t="n">
         <v>4039.47993593959</v>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M285" t="n">
-        <v>4131.3505859375</v>
       </c>
     </row>
     <row r="286">
@@ -13100,16 +13100,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K286" t="n">
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
+        <v>4130.16064453125</v>
+      </c>
+      <c r="M286" t="n">
         <v>4039.52307581659</v>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M286" t="n">
-        <v>4130.16064453125</v>
       </c>
     </row>
     <row r="287">
@@ -13145,16 +13145,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K287" t="n">
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>4137.556640625</v>
+      </c>
+      <c r="M287" t="n">
         <v>4037.257738306</v>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M287" t="n">
-        <v>4137.556640625</v>
       </c>
     </row>
     <row r="288">
@@ -13190,16 +13190,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K288" t="n">
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>4136.38037109375</v>
+      </c>
+      <c r="M288" t="n">
         <v>4028.03288483668</v>
-      </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M288" t="n">
-        <v>4136.38037109375</v>
       </c>
     </row>
     <row r="289">
@@ -13235,16 +13235,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K289" t="n">
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>4134.91015625</v>
+      </c>
+      <c r="M289" t="n">
         <v>4035.8739691216</v>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M289" t="n">
-        <v>4134.91015625</v>
       </c>
     </row>
     <row r="290">
@@ -13280,16 +13280,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K290" t="n">
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>4132.3828125</v>
+      </c>
+      <c r="M290" t="n">
         <v>4037.91438651011</v>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M290" t="n">
-        <v>4132.3828125</v>
       </c>
     </row>
     <row r="291">
@@ -13325,16 +13325,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K291" t="n">
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>4130.3759765625</v>
+      </c>
+      <c r="M291" t="n">
         <v>4046.21535505634</v>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M291" t="n">
-        <v>4130.3759765625</v>
       </c>
     </row>
     <row r="292">
@@ -13370,16 +13370,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K292" t="n">
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>4126.5849609375</v>
+      </c>
+      <c r="M292" t="n">
         <v>4027.58732564904</v>
-      </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M292" t="n">
-        <v>4126.5849609375</v>
       </c>
     </row>
     <row r="293">
@@ -13415,16 +13415,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K293" t="n">
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>4128.55517578125</v>
+      </c>
+      <c r="M293" t="n">
         <v>4030.88176327892</v>
-      </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M293" t="n">
-        <v>4128.55517578125</v>
       </c>
     </row>
     <row r="294">
@@ -13460,16 +13460,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K294" t="n">
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
+        <v>4126.15234375</v>
+      </c>
+      <c r="M294" t="n">
         <v>4032.14220510502</v>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M294" t="n">
-        <v>4126.15234375</v>
       </c>
     </row>
     <row r="295">
@@ -13505,16 +13505,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K295" t="n">
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>4124.763671875</v>
+      </c>
+      <c r="M295" t="n">
         <v>4046.18110660437</v>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M295" t="n">
-        <v>4124.763671875</v>
       </c>
     </row>
     <row r="296">
@@ -13550,16 +13550,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K296" t="n">
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>4129.3232421875</v>
+      </c>
+      <c r="M296" t="n">
         <v>4050.53576434114</v>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M296" t="n">
-        <v>4129.3232421875</v>
       </c>
     </row>
     <row r="297">
@@ -13595,16 +13595,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K297" t="n">
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>4136.9404296875</v>
+      </c>
+      <c r="M297" t="n">
         <v>4046.2573423412</v>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M297" t="n">
-        <v>4136.9404296875</v>
       </c>
     </row>
     <row r="298">
@@ -13640,16 +13640,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K298" t="n">
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
+        <v>4141.30615234375</v>
+      </c>
+      <c r="M298" t="n">
         <v>4038.83086191235</v>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M298" t="n">
-        <v>4141.30615234375</v>
       </c>
     </row>
     <row r="299">
@@ -13685,16 +13685,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K299" t="n">
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>4144.830078125</v>
+      </c>
+      <c r="M299" t="n">
         <v>4047.33024096157</v>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M299" t="n">
-        <v>4144.830078125</v>
       </c>
     </row>
     <row r="300">
@@ -13730,16 +13730,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K300" t="n">
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
+        <v>4147.03125</v>
+      </c>
+      <c r="M300" t="n">
         <v>4045.1228623697</v>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M300" t="n">
-        <v>4147.03125</v>
       </c>
     </row>
     <row r="301">
@@ -13775,16 +13775,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K301" t="n">
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
+        <v>4150.15576171875</v>
+      </c>
+      <c r="M301" t="n">
         <v>4057.56460048391</v>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M301" t="n">
-        <v>4150.15576171875</v>
       </c>
     </row>
     <row r="302">
@@ -13820,16 +13820,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K302" t="n">
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L302" t="n">
+        <v>4153.7421875</v>
+      </c>
+      <c r="M302" t="n">
         <v>4038.60857628658</v>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M302" t="n">
-        <v>4153.7421875</v>
       </c>
     </row>
     <row r="303">
@@ -13865,16 +13865,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K303" t="n">
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
+        <v>4151.5419921875</v>
+      </c>
+      <c r="M303" t="n">
         <v>4048.0129048167</v>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M303" t="n">
-        <v>4151.5419921875</v>
       </c>
     </row>
     <row r="304">
@@ -13910,16 +13910,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K304" t="n">
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L304" t="n">
+        <v>4150.5048828125</v>
+      </c>
+      <c r="M304" t="n">
         <v>4049.84058662856</v>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M304" t="n">
-        <v>4150.5048828125</v>
       </c>
     </row>
     <row r="305">
@@ -13955,16 +13955,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K305" t="n">
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
+        <v>4145.115234375</v>
+      </c>
+      <c r="M305" t="n">
         <v>4061.00344144252</v>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M305" t="n">
-        <v>4145.115234375</v>
       </c>
     </row>
     <row r="306">
@@ -14000,16 +14000,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K306" t="n">
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
+        <v>4141.8212890625</v>
+      </c>
+      <c r="M306" t="n">
         <v>4057.36339082858</v>
-      </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M306" t="n">
-        <v>4141.8212890625</v>
       </c>
     </row>
     <row r="307">
@@ -14045,16 +14045,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K307" t="n">
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
+        <v>4137.9765625</v>
+      </c>
+      <c r="M307" t="n">
         <v>4060.09701005745</v>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M307" t="n">
-        <v>4137.9765625</v>
       </c>
     </row>
     <row r="308">
@@ -14090,16 +14090,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K308" t="n">
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L308" t="n">
+        <v>4139.56640625</v>
+      </c>
+      <c r="M308" t="n">
         <v>4057.32370872798</v>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M308" t="n">
-        <v>4139.56640625</v>
       </c>
     </row>
     <row r="309">
@@ -14135,16 +14135,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K309" t="n">
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
+        <v>4140.69287109375</v>
+      </c>
+      <c r="M309" t="n">
         <v>4059.61835500997</v>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M309" t="n">
-        <v>4140.69287109375</v>
       </c>
     </row>
     <row r="310">
@@ -14180,16 +14180,16 @@
           <t>800by3000by23</t>
         </is>
       </c>
-      <c r="K310" t="n">
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>final validation</t>
+        </is>
+      </c>
+      <c r="L310" t="n">
+        <v>4141.228515625</v>
+      </c>
+      <c r="M310" t="n">
         <v>4063.52333715862</v>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>final validation</t>
-        </is>
-      </c>
-      <c r="M310" t="n">
-        <v>4141.228515625</v>
       </c>
     </row>
   </sheetData>
